--- a/artfynd/A 30353-2021 artfynd.xlsx
+++ b/artfynd/A 30353-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30353-2021 artfynd.xlsx
+++ b/artfynd/A 30353-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>748937</v>
+        <v>528348</v>
       </c>
       <c r="B3" t="n">
-        <v>92938</v>
+        <v>100451</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,24 +808,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>6002920</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Avarönn (aggregat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sorbus teodori agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åbro, Srm</t>
@@ -838,7 +843,7 @@
         <v>6522631.674610805</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +883,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flerstammigt, äldre träd av okänt ursprung</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3923747</v>
+        <v>748937</v>
       </c>
       <c r="B4" t="n">
-        <v>99381</v>
+        <v>92938</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +931,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221223</v>
+        <v>2779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1026,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6247719</v>
+        <v>3923747</v>
       </c>
       <c r="B5" t="n">
-        <v>101691</v>
+        <v>99381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,19 +1052,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224416</v>
+        <v>221223</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ljus solvända</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium subsp. nummularium</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1139,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67181721</v>
+        <v>6247719</v>
       </c>
       <c r="B6" t="n">
-        <v>100451</v>
+        <v>101691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,57 +1165,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6037534</v>
+        <v>224416</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avarönn</t>
+          <t>Ljus solvända</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sorbus teodori</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Liljef.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Helianthemum nummularium subsp. nummularium</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Åbro, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622927.757825554</v>
+        <v>622929.9882965996</v>
       </c>
       <c r="R6" t="n">
-        <v>6522620.204845677</v>
+        <v>6522631.674610805</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,7 +1219,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-08-17</t>
+          <t>2009-05-29</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1235,7 +1229,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-08-17</t>
+          <t>2009-05-29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1243,33 +1237,166 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Många torra grenar, men den sätter fortfarande frukt på de flesta. Kommer möjligtvis några nya grenar nertill.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>liten kalkklippa</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>67181721</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6037534</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Avarönn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sorbus teodori</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Liljef.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åbro, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>622927.757825554</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6522620.204845677</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Svärta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-08-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-08-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många torra grenar, men den sätter fortfarande frukt på de flesta. Kommer möjligtvis några nya grenar nertill.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Anton Johansson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Anton Johansson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
